--- a/real-estate-roi/output/deal_underwriting.xlsx
+++ b/real-estate-roi/output/deal_underwriting.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,9 +43,6 @@
     </font>
     <font>
       <color rgb="000F172A"/>
-    </font>
-    <font>
-      <color rgb="001D4ED8"/>
     </font>
     <font>
       <b val="1"/>
@@ -86,25 +83,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -659,7 +653,7 @@
           <t>Stabilized NOI</t>
         </is>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="4">
         <f>Assumptions!B5*(1+Assumptions!B9)</f>
         <v/>
       </c>
@@ -670,7 +664,7 @@
           <t>Total cost</t>
         </is>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="4">
         <f>Assumptions!B4*(1+Assumptions!B13)+Assumptions!B12</f>
         <v/>
       </c>
@@ -681,7 +675,7 @@
           <t>Loan</t>
         </is>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <f>Assumptions!B15*Assumptions!B4</f>
         <v/>
       </c>
@@ -692,7 +686,7 @@
           <t>Equity invested</t>
         </is>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="4">
         <f>B4-B5</f>
         <v/>
       </c>
@@ -703,7 +697,7 @@
           <t>Debt service (IO)</t>
         </is>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="4">
         <f>B5*Assumptions!B16</f>
         <v/>
       </c>
@@ -714,7 +708,7 @@
           <t>Debt yield</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="7">
         <f>Assumptions!B5/B5</f>
         <v/>
       </c>
@@ -725,43 +719,43 @@
           <t>LTC</t>
         </is>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="7">
         <f>B5/B4</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -773,23 +767,23 @@
           <t>NOI</t>
         </is>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="4">
         <f>IF(1&lt;=Assumptions!B10,Assumptions!B5+($B$3-Assumptions!B5)*1/Assumptions!B10,$B$3*(1+Assumptions!B11)^(1-Assumptions!B10))</f>
         <v/>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="4">
         <f>IF(2&lt;=Assumptions!B10,Assumptions!B5+($B$3-Assumptions!B5)*2/Assumptions!B10,$B$3*(1+Assumptions!B11)^(2-Assumptions!B10))</f>
         <v/>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="4">
         <f>IF(3&lt;=Assumptions!B10,Assumptions!B5+($B$3-Assumptions!B5)*3/Assumptions!B10,$B$3*(1+Assumptions!B11)^(3-Assumptions!B10))</f>
         <v/>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="4">
         <f>IF(4&lt;=Assumptions!B10,Assumptions!B5+($B$3-Assumptions!B5)*4/Assumptions!B10,$B$3*(1+Assumptions!B11)^(4-Assumptions!B10))</f>
         <v/>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="4">
         <f>IF(5&lt;=Assumptions!B10,Assumptions!B5+($B$3-Assumptions!B5)*5/Assumptions!B10,$B$3*(1+Assumptions!B11)^(5-Assumptions!B10))</f>
         <v/>
       </c>
@@ -800,76 +794,76 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="10">
         <f>C12/$B$7</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="10">
         <f>D12/$B$7</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="10">
         <f>E12/$B$7</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="10">
         <f>F12/$B$7</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="10">
         <f>G12/$B$7</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Equity cash flow</t>
         </is>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="4">
         <f>-B6</f>
         <v/>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="4">
         <f>C12-$B$7</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="4">
         <f>D12-$B$7</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="4">
         <f>E12-$B$7</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="4">
         <f>F12-$B$7</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="4">
         <f>G12-$B$7+(($B$3*(1+Assumptions!B11)^(5+1-Assumptions!B10))/Assumptions!B7*(1-Assumptions!B14)-B5)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="11">
         <f>IRR(B14:G14)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Equity multiple</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="12">
         <f>SUM(C14:G14)/B6</f>
         <v/>
       </c>
@@ -913,37 +907,37 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -955,27 +949,27 @@
           <t>Equity cash flow</t>
         </is>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <f>Underwriting!B14</f>
         <v/>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="4">
         <f>Underwriting!C14</f>
         <v/>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="4">
         <f>Underwriting!D14</f>
         <v/>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="4">
         <f>Underwriting!E14</f>
         <v/>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="4">
         <f>Underwriting!F14</f>
         <v/>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="4">
         <f>Underwriting!G14</f>
         <v/>
       </c>
@@ -1036,49 +1030,49 @@
           <t>Check (LP+GP−CF)</t>
         </is>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="4">
         <f>B6+B7-B5</f>
         <v/>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="4">
         <f>C6+C7-C5</f>
         <v/>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="4">
         <f>D6+D7-D5</f>
         <v/>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="4">
         <f>E6+E7-E5</f>
         <v/>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="4">
         <f>F6+F7-F5</f>
         <v/>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="4">
         <f>G6+G7-G5</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Project IRR</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="5">
         <f>IRR(B5:G5)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>LP IRR</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="11">
         <f>IRR(B6:G6)</f>
         <v/>
       </c>
@@ -1089,18 +1083,18 @@
           <t>LP equity multiple</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <f>SUM(C6:G6)/-B6</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>GP promote (total)</t>
         </is>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="13">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
@@ -1111,7 +1105,7 @@
           <t>GP share of profit</t>
         </is>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="7">
         <f>B13/SUM(C5:G5)</f>
         <v/>
       </c>
@@ -1154,7 +1148,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>exit\uplift</t>
         </is>

--- a/real-estate-roi/output/deal_underwriting.xlsx
+++ b/real-estate-roi/output/deal_underwriting.xlsx
@@ -482,7 +482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = input. Edit and the Underwriting tab recalculates.</t>
+          <t>Edit these inputs and the Underwriting tab recalculates.</t>
         </is>
       </c>
     </row>
